--- a/Промежуточная таблица 1.xlsx
+++ b/Промежуточная таблица 1.xlsx
@@ -71,10 +71,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -3714,39 +3715,45 @@
           <t>ДО: ДО1</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4156,21 +4163,21 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n">
         <v>4303</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>1996</v>
       </c>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4178,39 +4185,45 @@
           <t>ДО: ДО2</t>
         </is>
       </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4527,21 +4540,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n">
         <v>2493</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>1021</v>
       </c>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4549,39 +4562,45 @@
           <t>ДО: ДО3</t>
         </is>
       </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4898,21 +4917,21 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n">
         <v>4521</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>1296</v>
       </c>
-      <c r="G44" s="4" t="n"/>
+      <c r="G44" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4920,39 +4939,45 @@
           <t>ДО: ДО4</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -5269,21 +5294,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n">
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n">
         <v>2873</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="5" t="n">
         <v>1215</v>
       </c>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5291,39 +5316,45 @@
           <t>ДО: ДО5</t>
         </is>
       </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -5640,21 +5671,21 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n">
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n">
         <v>3147</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="5" t="n">
         <v>971</v>
       </c>
-      <c r="G72" s="4" t="n"/>
+      <c r="G72" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5662,39 +5693,45 @@
           <t>ДО: ДО6</t>
         </is>
       </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6011,21 +6048,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n">
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n">
         <v>2973</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="5" t="n">
         <v>1589</v>
       </c>
-      <c r="G86" s="4" t="n"/>
+      <c r="G86" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6033,39 +6070,45 @@
           <t>ДО: ДО7</t>
         </is>
       </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6382,21 +6425,21 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n">
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n">
         <v>3342</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="5" t="n">
         <v>1728</v>
       </c>
-      <c r="G100" s="4" t="n"/>
+      <c r="G100" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6404,39 +6447,45 @@
           <t>ДО: ДО8</t>
         </is>
       </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6753,21 +6802,21 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n">
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n">
         <v>4073</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="5" t="n">
         <v>798</v>
       </c>
-      <c r="G114" s="4" t="n"/>
+      <c r="G114" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6775,39 +6824,45 @@
           <t>ДО: ДО9</t>
         </is>
       </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -7124,21 +7179,21 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n">
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n">
         <v>3936</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="5" t="n">
         <v>1248</v>
       </c>
-      <c r="G128" s="4" t="n"/>
+      <c r="G128" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7146,39 +7201,45 @@
           <t>ДО: ДО10</t>
         </is>
       </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -7495,35 +7556,23 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B142" s="4" t="n"/>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n">
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n">
         <v>3655</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="5" t="n">
         <v>1086</v>
       </c>
-      <c r="G142" s="4" t="n"/>
+      <c r="G142" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A102:G102"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A116:G116"/>
-    <mergeCell ref="A130:G130"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A46:G46"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>